--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.59775807047235</v>
+        <v>8.384635686451757</v>
       </c>
       <c r="D2" t="n">
-        <v>51.62866186584611</v>
+        <v>8.389657553199994</v>
       </c>
       <c r="E2" t="n">
-        <v>3.602740793822361</v>
+        <v>0.585445378996134</v>
       </c>
       <c r="F2" t="n">
-        <v>3.654625674739791</v>
+        <v>0.5938766721452161</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.5425168604182</v>
+        <v>6.750658989817958</v>
       </c>
       <c r="D3" t="n">
-        <v>41.50315330134339</v>
+        <v>6.744262411468301</v>
       </c>
       <c r="E3" t="n">
-        <v>3.602740793822361</v>
+        <v>0.585445378996134</v>
       </c>
       <c r="F3" t="n">
-        <v>3.654625674739791</v>
+        <v>0.5938766721452161</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.09982562253179</v>
+        <v>7.491221663661416</v>
       </c>
       <c r="D4" t="n">
-        <v>45.65284792433722</v>
+        <v>7.418587787704798</v>
       </c>
       <c r="E4" t="n">
-        <v>3.602740793822361</v>
+        <v>0.585445378996134</v>
       </c>
       <c r="F4" t="n">
-        <v>3.654625674739791</v>
+        <v>0.5938766721452161</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.68750177892256</v>
+        <v>7.749219039074916</v>
       </c>
       <c r="D5" t="n">
-        <v>47.72506983499051</v>
+        <v>7.755323848185959</v>
       </c>
       <c r="E5" t="n">
-        <v>3.602740793822361</v>
+        <v>0.585445378996134</v>
       </c>
       <c r="F5" t="n">
-        <v>3.654625674739791</v>
+        <v>0.5938766721452161</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
